--- a/artfynd/A 8807-2022 artfynd.xlsx
+++ b/artfynd/A 8807-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,224 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121915059</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91133</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skarabergsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>409386</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6475046</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121915061</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91343</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skarabergsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>409353</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6475147</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8807-2022 artfynd.xlsx
+++ b/artfynd/A 8807-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,6 +998,113 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121963294</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91343</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skarabergsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>409386</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6475046</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8807-2022 artfynd.xlsx
+++ b/artfynd/A 8807-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121915059</v>
+        <v>121915061</v>
       </c>
       <c r="B3" t="n">
-        <v>91133</v>
+        <v>91343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409386</v>
+        <v>409353</v>
       </c>
       <c r="R3" t="n">
-        <v>6475046</v>
+        <v>6475147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +869,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121915061</v>
+        <v>121915059</v>
       </c>
       <c r="B4" t="n">
-        <v>91343</v>
+        <v>91133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,37 +909,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409353</v>
+        <v>409386</v>
       </c>
       <c r="R4" t="n">
-        <v>6475147</v>
+        <v>6475046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +977,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8807-2022 artfynd.xlsx
+++ b/artfynd/A 8807-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121915061</v>
+        <v>121915059</v>
       </c>
       <c r="B3" t="n">
-        <v>91343</v>
+        <v>91147</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409353</v>
+        <v>409386</v>
       </c>
       <c r="R3" t="n">
-        <v>6475147</v>
+        <v>6475046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121915059</v>
+        <v>121915061</v>
       </c>
       <c r="B4" t="n">
-        <v>91133</v>
+        <v>91357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,34 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409386</v>
+        <v>409353</v>
       </c>
       <c r="R4" t="n">
-        <v>6475046</v>
+        <v>6475147</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +976,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>121963294</v>
       </c>
       <c r="B5" t="n">
-        <v>91343</v>
+        <v>91357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 8807-2022 artfynd.xlsx
+++ b/artfynd/A 8807-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>121915059</v>
       </c>
       <c r="B3" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>121915061</v>
       </c>
       <c r="B4" t="n">
-        <v>91357</v>
+        <v>91359</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>121963294</v>
       </c>
       <c r="B5" t="n">
-        <v>91357</v>
+        <v>91359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 8807-2022 artfynd.xlsx
+++ b/artfynd/A 8807-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121915059</v>
+        <v>121915061</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
+        <v>91394</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409386</v>
+        <v>409353</v>
       </c>
       <c r="R3" t="n">
-        <v>6475046</v>
+        <v>6475147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +869,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121915061</v>
+        <v>121915059</v>
       </c>
       <c r="B4" t="n">
-        <v>91394</v>
+        <v>91184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,37 +909,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409353</v>
+        <v>409386</v>
       </c>
       <c r="R4" t="n">
-        <v>6475147</v>
+        <v>6475046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +977,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8807-2022 artfynd.xlsx
+++ b/artfynd/A 8807-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121915061</v>
+        <v>121915059</v>
       </c>
       <c r="B3" t="n">
-        <v>91394</v>
+        <v>91194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409353</v>
+        <v>409386</v>
       </c>
       <c r="R3" t="n">
-        <v>6475147</v>
+        <v>6475046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121915059</v>
+        <v>121915061</v>
       </c>
       <c r="B4" t="n">
-        <v>91184</v>
+        <v>91404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,34 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409386</v>
+        <v>409353</v>
       </c>
       <c r="R4" t="n">
-        <v>6475046</v>
+        <v>6475147</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +976,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>121963294</v>
       </c>
       <c r="B5" t="n">
-        <v>91394</v>
+        <v>91404</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 8807-2022 artfynd.xlsx
+++ b/artfynd/A 8807-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116487430</v>
+        <v>121915061</v>
       </c>
       <c r="B2" t="n">
-        <v>96724</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Esstorp NO, Skara stifts skogsmarker, Vg</t>
+          <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409458</v>
+        <v>409353</v>
       </c>
       <c r="R2" t="n">
-        <v>6475098</v>
+        <v>6475147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,12 +757,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -775,22 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Solveig Svensson, Jon Liljebäck</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121915059</v>
+        <v>121963294</v>
       </c>
       <c r="B3" t="n">
-        <v>91194</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +865,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -882,22 +876,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121915061</v>
+        <v>121915059</v>
       </c>
       <c r="B4" t="n">
-        <v>91404</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,37 +894,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarabergsskogen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409353</v>
+        <v>409386</v>
       </c>
       <c r="R4" t="n">
-        <v>6475147</v>
+        <v>6475046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +962,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1000,15 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121963294</v>
+        <v>116487430</v>
       </c>
       <c r="B5" t="n">
-        <v>91404</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,34 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarabergsskogen, Vg</t>
+          <t>Esstorp NO, Skara stifts skogsmarker, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409386</v>
+        <v>409458</v>
       </c>
       <c r="R5" t="n">
-        <v>6475046</v>
+        <v>6475098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,12 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,7 +1080,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Solveig Svensson, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 8807-2022 artfynd.xlsx
+++ b/artfynd/A 8807-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121915061</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121963294</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121915059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,8 +1104,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116487430</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>